--- a/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Inversion Inicial'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PyG 3 Anos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Punto Equilibrio'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Escenarios'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Personal'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -512,7 +518,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -543,6 +549,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -894,7 +901,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -902,7 +918,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -928,6 +944,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1491,7 +1508,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1499,7 +1525,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1516,6 +1542,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1676,7 +1704,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1684,7 +1721,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1702,6 +1739,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1894,7 +1933,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1902,7 +1950,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1922,6 +1970,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2098,7 +2148,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2106,9 +2165,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2123,6 +2182,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2341,6 +2401,14 @@
       <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Mas lento que cafeteria por mayor inversion en maquinaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-panaderia · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -2348,6 +2416,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>